--- a/app-assets/templates/Timesheet_ATO.xlsx
+++ b/app-assets/templates/Timesheet_ATO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANDERS~1.MAR\AppData\Local\Temp\claude\C--Users-anderson-marley-Documents-01---Desenvolvimento-sistema-gestao-medicoes\7c498f8a-a560-48db-9bf4-de0aad30ae7b\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F8F23AB-9086-463A-B805-9F49995C979B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2371E07-F020-44E4-B174-A75A77EA8C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="509" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
@@ -80,48 +80,6 @@
   </si>
   <si>
     <t>Contrato N.º:</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Tipo de Serviço</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>: ATO</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Contratada: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Projeta Consultoria</t>
-    </r>
   </si>
   <si>
     <t>Nº da SE:</t>
@@ -183,12 +141,54 @@
   <si>
     <t>Doc. N.º:</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0F172A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Tipo de Serviço</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F172A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: ATO</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0F172A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Contratada: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F172A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Projeta Consultoria</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -203,11 +203,12 @@
     <numFmt numFmtId="174" formatCode="h:mm;@"/>
     <numFmt numFmtId="175" formatCode="[$-416]d\-mmm;@"/>
     <numFmt numFmtId="176" formatCode="[h]:mm:ss;@"/>
-    <numFmt numFmtId="178" formatCode="[h]:mm"/>
-    <numFmt numFmtId="179" formatCode="&quot;R$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="180" formatCode="&quot;Funcionário: &quot;@"/>
+    <numFmt numFmtId="177" formatCode="[h]:mm"/>
+    <numFmt numFmtId="178" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="179" formatCode="&quot;Funcionário: &quot;@"/>
+    <numFmt numFmtId="180" formatCode="dd/mm/yyyy\ ddd"/>
   </numFmts>
-  <fonts count="44" x14ac:knownFonts="1">
+  <fonts count="47" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,12 +288,6 @@
       <family val="3"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
@@ -427,19 +422,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
@@ -454,53 +436,94 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF0F172A"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <color theme="1"/>
+      <color rgb="FF0F172A"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF0F172A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0F172A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0F172A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0F172A"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF64748B"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF007E7A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF475569"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF475569"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF007E7A"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="7"/>
+      <color rgb="FF64748B"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -692,30 +715,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC0C0C0"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor rgb="FF007E7A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
+        <fgColor rgb="FFF1F5F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFF8FAFC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -736,463 +759,6 @@
       <bottom style="thin">
         <color indexed="22"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1319,15 +885,217 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCBD5E1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FFCBD5E1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1E293B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1E293B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1E293B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1335,41 +1103,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="42" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1382,7 +1150,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="170" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1390,17 +1158,17 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="45" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="171" fontId="6" fillId="0" borderId="0">
@@ -1413,46 +1181,46 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="46" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="47" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="48" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="49" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="173" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="173" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="50" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="55"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="55" applyFont="1"/>
@@ -1482,198 +1250,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="55" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="55" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="34" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="31" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="33" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="34" borderId="34" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="55" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="33" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="13" fillId="36" borderId="14" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="55" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="35" borderId="14" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="20" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="55" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="4" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="37" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="17" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="18" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="21" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="11" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="12" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="55" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="55" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="55" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="55" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="55" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="7" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="55" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="55" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="55" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="55" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="55" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="25" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="17" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="11" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="55" applyAlignment="1" applyProtection="1">
@@ -1687,272 +1278,373 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="55" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="14" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="39" fillId="0" borderId="0" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="55" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="55" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="34" borderId="12" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="34" borderId="33" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="34" borderId="13" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="34" borderId="34" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="34" borderId="12" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="38" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="33" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="23" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="34" borderId="18" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="11" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="22" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="34" borderId="17" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="8" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="19" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="34" fillId="0" borderId="18" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="34" fillId="0" borderId="20" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="21" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="18" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="2" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="9" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="36" fillId="0" borderId="18" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="36" fillId="0" borderId="20" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="19" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="17" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="21" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="19" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="21" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="36" fillId="0" borderId="16" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="37" fillId="0" borderId="19" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="17" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="19" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="17" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="21" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="13" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="12" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="21" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="37" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="39" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="5" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="26" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="37" borderId="33" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="174" fontId="37" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="37" borderId="4" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="177" fontId="36" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="15" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="19" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="26" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="35" fillId="0" borderId="17" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="35" fillId="0" borderId="19" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="39" fillId="0" borderId="0" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="39" fillId="0" borderId="15" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="43" fontId="39" fillId="0" borderId="13" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="13" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="43" fontId="39" fillId="0" borderId="13" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="39" fillId="0" borderId="14" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="38" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="27" xfId="55" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="20" xfId="55" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="55" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="18" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="37" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="18" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="37" fillId="0" borderId="20" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="23" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="23" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="24" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="35" borderId="16" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="40" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="35" borderId="17" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="33" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="12" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="0" borderId="15" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="33" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="0" borderId="13" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="42" fillId="0" borderId="14" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="36" borderId="15" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="34" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="36" borderId="12" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="12" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="33" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="36" borderId="12" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="34" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="36" borderId="25" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="27" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="36" borderId="16" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="51" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="43" fillId="36" borderId="17" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="17" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="23" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="12" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="37" fillId="0" borderId="8" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="37" fillId="0" borderId="24" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="25" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="35" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="10" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="8" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="43" fillId="36" borderId="17" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="9" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="36" borderId="26" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="40" fillId="0" borderId="8" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="40" fillId="0" borderId="24" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="34" borderId="14" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="180" fontId="37" fillId="0" borderId="16" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="34" borderId="4" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="43" fontId="39" fillId="0" borderId="27" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="39" fillId="0" borderId="20" xfId="92" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="175" fontId="36" fillId="37" borderId="28" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="36" fillId="37" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="34" borderId="40" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="176" fontId="37" fillId="37" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="34" borderId="34" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="178" fontId="36" fillId="37" borderId="29" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="32" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="28" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="30" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="31" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="26" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="180" fontId="40" fillId="0" borderId="36" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="180" fontId="41" fillId="0" borderId="28" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="180" fontId="41" fillId="0" borderId="29" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="28" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="55" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="37" borderId="29" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="37" borderId="30" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="55" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="26" xfId="55" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="55" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="55" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="55" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="55" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="177" fontId="45" fillId="37" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="27" xfId="55" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="22" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2060,11 +1752,11 @@
       <font>
         <b/>
         <i val="0"/>
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FF14532D"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF808080"/>
+          <bgColor rgb="FFE6F4EA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2072,11 +1764,11 @@
       <font>
         <b/>
         <i val="0"/>
-        <color theme="0"/>
+        <color rgb="FF14532D"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
+          <bgColor rgb="FFE6F4EA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2191,8 +1883,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="15066980" y="21671803"/>
-          <a:ext cx="898197" cy="0"/>
+          <a:off x="15311908" y="21671803"/>
+          <a:ext cx="898198" cy="0"/>
           <a:chOff x="330" y="994"/>
           <a:chExt cx="88" cy="15"/>
         </a:xfrm>
@@ -2345,7 +2037,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7121413" y="21658195"/>
+          <a:off x="7366342" y="21658195"/>
           <a:ext cx="1024890" cy="0"/>
           <a:chOff x="330" y="994"/>
           <a:chExt cx="88" cy="15"/>
@@ -3070,12 +2762,12 @@
   <dimension ref="A1:AB54"/>
   <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="8.5546875" style="1" customWidth="1"/>
     <col min="6" max="9" width="15.33203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="36.44140625" style="1" customWidth="1"/>
-    <col min="11" max="13" width="24.33203125" style="71" customWidth="1"/>
+    <col min="11" max="13" width="24.33203125" style="22" customWidth="1"/>
     <col min="14" max="14" width="16" style="1" customWidth="1"/>
     <col min="15" max="15" width="8.5546875" style="1" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="8.5546875" style="7" hidden="1" customWidth="1"/>
@@ -3087,237 +2779,237 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="2" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="e" vm="1">
+      <c r="A1" s="32" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="79" t="e" vm="2">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="29" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="102" t="s">
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="103"/>
+      <c r="N1" s="31"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="4"/>
       <c r="R1" s="7"/>
       <c r="S1" s="4"/>
     </row>
     <row r="2" spans="1:19" s="2" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="104"/>
-      <c r="N2" s="105"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="42"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="7"/>
       <c r="S2" s="4"/>
     </row>
     <row r="3" spans="1:19" s="2" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="106" t="s">
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="107"/>
-      <c r="M3" s="108" t="s">
-        <v>24</v>
+      <c r="L3" s="40"/>
+      <c r="M3" s="94" t="s">
+        <v>22</v>
       </c>
-      <c r="N3" s="109"/>
+      <c r="N3" s="43"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="7"/>
       <c r="S3" s="4"/>
     </row>
     <row r="4" spans="1:19" s="2" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="118"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="113"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="47"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="7"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" spans="1:19" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="51"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="18"/>
+    </row>
+    <row r="6" spans="1:19" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="87"/>
-      <c r="M5" s="114" t="s">
-        <v>23</v>
-      </c>
-      <c r="N5" s="115"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="23"/>
-    </row>
-    <row r="6" spans="1:19" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="85" t="s">
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="86"/>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="120" t="s">
+      <c r="N6" s="54"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="18"/>
+    </row>
+    <row r="7" spans="1:19" s="10" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="55"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="60"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="18"/>
+    </row>
+    <row r="8" spans="1:19" s="10" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="61"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="57"/>
+      <c r="N8" s="64"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="18"/>
+    </row>
+    <row r="9" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="95"/>
+      <c r="B9" s="96"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="97"/>
+    </row>
+    <row r="10" spans="1:19" s="3" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="128"/>
-      <c r="L6" s="129"/>
-      <c r="M6" s="120" t="s">
+      <c r="B10" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="121"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="23"/>
-    </row>
-    <row r="7" spans="1:19" s="10" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="130"/>
-      <c r="B7" s="131"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="126"/>
-      <c r="K7" s="133"/>
-      <c r="L7" s="134"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="30"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="23"/>
-    </row>
-    <row r="8" spans="1:19" s="10" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="122"/>
-      <c r="B8" s="123"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="123"/>
-      <c r="H8" s="123"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="125"/>
-      <c r="K8" s="123"/>
-      <c r="L8" s="124"/>
-      <c r="M8" s="126"/>
-      <c r="N8" s="127"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="23"/>
-    </row>
-    <row r="9" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="90"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="91"/>
-      <c r="K9" s="91"/>
-      <c r="L9" s="91"/>
-      <c r="M9" s="91"/>
-      <c r="N9" s="92"/>
-    </row>
-    <row r="10" spans="1:19" s="3" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="93" t="s">
+      <c r="C10" s="99"/>
+      <c r="D10" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="95" t="s">
+      <c r="E10" s="99"/>
+      <c r="F10" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95" t="s">
+      <c r="G10" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="95"/>
-      <c r="F10" s="73" t="s">
+      <c r="H10" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="73" t="s">
+      <c r="I10" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="73" t="s">
+      <c r="J10" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="96" t="s">
+      <c r="L10" s="101"/>
+      <c r="M10" s="101"/>
+      <c r="N10" s="102" t="s">
         <v>13</v>
-      </c>
-      <c r="J10" s="98" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="96" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="100" t="s">
-        <v>15</v>
       </c>
       <c r="P10" s="6"/>
       <c r="Q10" s="4"/>
@@ -3325,833 +3017,882 @@
       <c r="S10" s="4"/>
     </row>
     <row r="11" spans="1:19" s="3" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="94"/>
-      <c r="B11" s="18" t="s">
-        <v>16</v>
+      <c r="A11" s="103"/>
+      <c r="B11" s="104" t="s">
+        <v>14</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>17</v>
+      <c r="C11" s="104" t="s">
+        <v>15</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>16</v>
+      <c r="D11" s="104" t="s">
+        <v>14</v>
       </c>
-      <c r="E11" s="18" t="s">
-        <v>17</v>
+      <c r="E11" s="104" t="s">
+        <v>15</v>
       </c>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="97"/>
-      <c r="J11" s="99"/>
-      <c r="K11" s="97"/>
-      <c r="L11" s="97"/>
-      <c r="M11" s="97"/>
-      <c r="N11" s="101"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="106"/>
+      <c r="J11" s="106"/>
+      <c r="K11" s="106"/>
+      <c r="L11" s="106"/>
+      <c r="M11" s="106"/>
+      <c r="N11" s="107"/>
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
       <c r="R11" s="7"/>
       <c r="S11" s="4"/>
     </row>
     <row r="12" spans="1:19" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="138"/>
-      <c r="L12" s="139"/>
-      <c r="M12" s="140"/>
-      <c r="N12" s="32"/>
+      <c r="A12" s="108"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="69"/>
+      <c r="L12" s="70"/>
+      <c r="M12" s="70"/>
+      <c r="N12" s="71"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="11"/>
       <c r="R12" s="5"/>
       <c r="S12" s="12"/>
     </row>
     <row r="13" spans="1:19" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="138"/>
-      <c r="L13" s="139"/>
-      <c r="M13" s="140"/>
-      <c r="N13" s="32"/>
+      <c r="A13" s="108"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="69"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="70"/>
+      <c r="N13" s="71"/>
       <c r="P13" s="5"/>
       <c r="Q13" s="11"/>
       <c r="R13" s="5"/>
       <c r="S13" s="12"/>
     </row>
     <row r="14" spans="1:19" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="135"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="137"/>
-      <c r="N14" s="32"/>
+      <c r="A14" s="108"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="71"/>
       <c r="P14" s="5"/>
       <c r="Q14" s="11"/>
       <c r="R14" s="5"/>
       <c r="S14" s="12"/>
     </row>
     <row r="15" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="135"/>
-      <c r="L15" s="136"/>
-      <c r="M15" s="137"/>
-      <c r="N15" s="32"/>
+      <c r="A15" s="108"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="71"/>
       <c r="Q15" s="8"/>
     </row>
     <row r="16" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="136"/>
-      <c r="M16" s="137"/>
-      <c r="N16" s="32"/>
+      <c r="A16" s="108"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="68"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="71"/>
       <c r="Q16" s="8"/>
     </row>
     <row r="17" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="135"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="137"/>
-      <c r="N17" s="32"/>
+      <c r="A17" s="108"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="71"/>
       <c r="Q17" s="8"/>
     </row>
     <row r="18" spans="1:19" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="135"/>
-      <c r="L18" s="136"/>
-      <c r="M18" s="137"/>
-      <c r="N18" s="32"/>
+      <c r="A18" s="108"/>
+      <c r="B18" s="65"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="66"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="73"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="71"/>
       <c r="P18" s="14"/>
       <c r="Q18" s="15"/>
       <c r="R18" s="14"/>
       <c r="S18" s="16"/>
     </row>
     <row r="19" spans="1:19" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="135"/>
-      <c r="L19" s="136"/>
-      <c r="M19" s="137"/>
-      <c r="N19" s="32"/>
+      <c r="A19" s="108"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="73"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="71"/>
       <c r="P19" s="14"/>
       <c r="Q19" s="15"/>
       <c r="R19" s="14"/>
       <c r="S19" s="16"/>
     </row>
     <row r="20" spans="1:19" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="26"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="135"/>
-      <c r="L20" s="136"/>
-      <c r="M20" s="137"/>
-      <c r="N20" s="32"/>
+      <c r="A20" s="108"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="71"/>
       <c r="P20" s="14"/>
       <c r="Q20" s="15"/>
       <c r="R20" s="14"/>
       <c r="S20" s="16"/>
     </row>
     <row r="21" spans="1:19" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="26"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="135"/>
-      <c r="L21" s="136"/>
-      <c r="M21" s="137"/>
-      <c r="N21" s="32"/>
+      <c r="A21" s="108"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="73"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="71"/>
       <c r="P21" s="14"/>
       <c r="Q21" s="15"/>
       <c r="R21" s="14"/>
       <c r="S21" s="16"/>
     </row>
     <row r="22" spans="1:19" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="26"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="135"/>
-      <c r="L22" s="136"/>
-      <c r="M22" s="137"/>
-      <c r="N22" s="32"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="71"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="15"/>
       <c r="R22" s="14"/>
       <c r="S22" s="16"/>
     </row>
     <row r="23" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="135"/>
-      <c r="L23" s="136"/>
-      <c r="M23" s="137"/>
-      <c r="N23" s="32"/>
+      <c r="A23" s="108"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="71"/>
       <c r="Q23" s="8"/>
     </row>
     <row r="24" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="26"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="135"/>
-      <c r="L24" s="136"/>
-      <c r="M24" s="137"/>
-      <c r="N24" s="32"/>
+      <c r="A24" s="108"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="73"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="71"/>
       <c r="Q24" s="8"/>
     </row>
     <row r="25" spans="1:19" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="26"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="135"/>
-      <c r="L25" s="136"/>
-      <c r="M25" s="137"/>
-      <c r="N25" s="32"/>
+      <c r="A25" s="108"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="71"/>
       <c r="P25" s="14"/>
       <c r="Q25" s="15"/>
       <c r="R25" s="14"/>
       <c r="S25" s="16"/>
     </row>
     <row r="26" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="26"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="135"/>
-      <c r="L26" s="136"/>
-      <c r="M26" s="137"/>
-      <c r="N26" s="32"/>
+      <c r="A26" s="108"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="73"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="71"/>
       <c r="Q26" s="8"/>
     </row>
     <row r="27" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="26"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="135"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="137"/>
-      <c r="N27" s="32"/>
+      <c r="A27" s="108"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="73"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="71"/>
       <c r="Q27" s="8"/>
     </row>
     <row r="28" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="26"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="135"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="137"/>
-      <c r="N28" s="32"/>
+      <c r="A28" s="108"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="73"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="71"/>
       <c r="Q28" s="8"/>
     </row>
     <row r="29" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="26"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="135"/>
-      <c r="L29" s="136"/>
-      <c r="M29" s="137"/>
-      <c r="N29" s="32"/>
+      <c r="A29" s="108"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="66"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="73"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="71"/>
       <c r="Q29" s="8"/>
     </row>
     <row r="30" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="26"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="135"/>
-      <c r="L30" s="136"/>
-      <c r="M30" s="137"/>
-      <c r="N30" s="32"/>
+      <c r="A30" s="108"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="66"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="68"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="73"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="71"/>
       <c r="Q30" s="8"/>
     </row>
     <row r="31" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="26"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="135"/>
-      <c r="L31" s="136"/>
-      <c r="M31" s="137"/>
-      <c r="N31" s="32"/>
+      <c r="A31" s="108"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="66"/>
+      <c r="G31" s="66"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="68"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="71"/>
       <c r="Q31" s="8"/>
     </row>
     <row r="32" spans="1:19" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="26"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="135"/>
-      <c r="L32" s="136"/>
-      <c r="M32" s="137"/>
-      <c r="N32" s="32"/>
+      <c r="A32" s="108"/>
+      <c r="B32" s="65"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="66"/>
+      <c r="G32" s="66"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="67"/>
+      <c r="J32" s="68"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="73"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="71"/>
       <c r="P32" s="5"/>
       <c r="Q32" s="11"/>
       <c r="R32" s="5"/>
       <c r="S32" s="12"/>
     </row>
     <row r="33" spans="1:28" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="26"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="135"/>
-      <c r="L33" s="136"/>
-      <c r="M33" s="137"/>
-      <c r="N33" s="32"/>
+      <c r="A33" s="108"/>
+      <c r="B33" s="65"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="66"/>
+      <c r="G33" s="66"/>
+      <c r="H33" s="66"/>
+      <c r="I33" s="67"/>
+      <c r="J33" s="68"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="73"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="71"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="11"/>
       <c r="R33" s="5"/>
       <c r="S33" s="12"/>
     </row>
     <row r="34" spans="1:28" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="26"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="135"/>
-      <c r="L34" s="136"/>
-      <c r="M34" s="137"/>
-      <c r="N34" s="32"/>
+      <c r="A34" s="108"/>
+      <c r="B34" s="65"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="66"/>
+      <c r="G34" s="66"/>
+      <c r="H34" s="66"/>
+      <c r="I34" s="67"/>
+      <c r="J34" s="68"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="73"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="71"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="11"/>
       <c r="R34" s="5"/>
       <c r="S34" s="12"/>
     </row>
     <row r="35" spans="1:28" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="26"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="135"/>
-      <c r="L35" s="136"/>
-      <c r="M35" s="137"/>
-      <c r="N35" s="32"/>
+      <c r="A35" s="108"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
+      <c r="H35" s="66"/>
+      <c r="I35" s="67"/>
+      <c r="J35" s="68"/>
+      <c r="K35" s="72"/>
+      <c r="L35" s="73"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="71"/>
       <c r="P35" s="5"/>
       <c r="Q35" s="11"/>
       <c r="R35" s="5"/>
       <c r="S35" s="12"/>
     </row>
     <row r="36" spans="1:28" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="26"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="135"/>
-      <c r="L36" s="136"/>
-      <c r="M36" s="137"/>
-      <c r="N36" s="32"/>
+      <c r="A36" s="108"/>
+      <c r="B36" s="65"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="66"/>
+      <c r="H36" s="66"/>
+      <c r="I36" s="67"/>
+      <c r="J36" s="68"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="73"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="71"/>
       <c r="P36" s="5"/>
       <c r="Q36" s="11"/>
       <c r="R36" s="5"/>
       <c r="S36" s="12"/>
     </row>
     <row r="37" spans="1:28" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="26"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="135"/>
-      <c r="L37" s="136"/>
-      <c r="M37" s="137"/>
-      <c r="N37" s="32"/>
+      <c r="A37" s="108"/>
+      <c r="B37" s="65"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="66"/>
+      <c r="G37" s="66"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="67"/>
+      <c r="J37" s="68"/>
+      <c r="K37" s="72"/>
+      <c r="L37" s="73"/>
+      <c r="M37" s="73"/>
+      <c r="N37" s="71"/>
       <c r="P37" s="5"/>
       <c r="Q37" s="11"/>
       <c r="R37" s="5"/>
       <c r="S37" s="12"/>
     </row>
     <row r="38" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="26"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="135"/>
-      <c r="L38" s="136"/>
-      <c r="M38" s="137"/>
-      <c r="N38" s="32"/>
+      <c r="A38" s="108"/>
+      <c r="B38" s="65"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="68"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="73"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="71"/>
       <c r="Q38" s="8"/>
     </row>
     <row r="39" spans="1:28" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="26"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="135"/>
-      <c r="L39" s="136"/>
-      <c r="M39" s="137"/>
-      <c r="N39" s="32"/>
+      <c r="A39" s="108"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="65"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="66"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="68"/>
+      <c r="K39" s="72"/>
+      <c r="L39" s="73"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="71"/>
       <c r="P39" s="5"/>
       <c r="Q39" s="11"/>
       <c r="R39" s="5"/>
       <c r="S39" s="12"/>
     </row>
     <row r="40" spans="1:28" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="26"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="135"/>
-      <c r="L40" s="136"/>
-      <c r="M40" s="137"/>
-      <c r="N40" s="32"/>
+      <c r="A40" s="108"/>
+      <c r="B40" s="65"/>
+      <c r="C40" s="65"/>
+      <c r="D40" s="65"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
+      <c r="H40" s="66"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="68"/>
+      <c r="K40" s="72"/>
+      <c r="L40" s="73"/>
+      <c r="M40" s="73"/>
+      <c r="N40" s="71"/>
       <c r="P40" s="5"/>
       <c r="Q40" s="11"/>
       <c r="R40" s="5"/>
       <c r="S40" s="12"/>
     </row>
     <row r="41" spans="1:28" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="26"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="135"/>
-      <c r="L41" s="136"/>
-      <c r="M41" s="137"/>
-      <c r="N41" s="32"/>
+      <c r="A41" s="108"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="72"/>
+      <c r="L41" s="73"/>
+      <c r="M41" s="73"/>
+      <c r="N41" s="71"/>
       <c r="P41" s="5"/>
       <c r="Q41" s="11"/>
       <c r="R41" s="5"/>
       <c r="S41" s="12"/>
     </row>
-    <row r="42" spans="1:28" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="72"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="135"/>
-      <c r="L42" s="136"/>
-      <c r="M42" s="137"/>
-      <c r="N42" s="32"/>
+    <row r="42" spans="1:28" s="2" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="108"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="66"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="68"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="73"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="71"/>
       <c r="P42" s="5"/>
       <c r="Q42" s="11"/>
       <c r="R42" s="5"/>
       <c r="S42" s="12"/>
     </row>
     <row r="43" spans="1:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="111" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="112"/>
+      <c r="C43" s="112"/>
+      <c r="D43" s="112"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="113"/>
+      <c r="G43" s="113"/>
+      <c r="H43" s="113"/>
+      <c r="I43" s="117"/>
+      <c r="J43" s="114"/>
+      <c r="K43" s="115"/>
+      <c r="L43" s="115"/>
+      <c r="M43" s="115"/>
+      <c r="N43" s="116"/>
+      <c r="Q43" s="8"/>
+    </row>
+    <row r="44" spans="1:28" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="109"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
+      <c r="J44" s="23"/>
+      <c r="K44" s="74"/>
+      <c r="L44" s="74"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="110"/>
+      <c r="Q44" s="7"/>
+      <c r="AB44" s="17"/>
+    </row>
+    <row r="45" spans="1:28" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="75"/>
+      <c r="B45" s="76"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="76"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="76"/>
+      <c r="I45" s="76"/>
+      <c r="J45" s="76"/>
+      <c r="K45" s="77"/>
+      <c r="L45" s="77"/>
+      <c r="M45" s="77"/>
+      <c r="N45" s="78"/>
+      <c r="Q45" s="7"/>
+      <c r="AB45" s="17"/>
+    </row>
+    <row r="46" spans="1:28" s="10" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="118" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" s="24"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="25"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="26"/>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="80"/>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="18"/>
+      <c r="R46" s="9"/>
+      <c r="S46" s="18"/>
+    </row>
+    <row r="47" spans="1:28" s="10" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="79"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="25"/>
+      <c r="J47" s="82"/>
+      <c r="K47" s="83"/>
+      <c r="L47" s="27"/>
+      <c r="M47" s="27"/>
+      <c r="N47" s="80"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="18"/>
+      <c r="R47" s="9"/>
+      <c r="S47" s="18"/>
+    </row>
+    <row r="48" spans="1:28" s="10" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="79"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="142"/>
-      <c r="L43" s="142"/>
-      <c r="M43" s="142"/>
-      <c r="N43" s="34"/>
-      <c r="Q43" s="8"/>
-    </row>
-    <row r="44" spans="1:28" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="35"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="59"/>
-      <c r="L44" s="59"/>
-      <c r="M44" s="59"/>
-      <c r="N44" s="37"/>
-      <c r="Q44" s="7"/>
-      <c r="AB44" s="19"/>
-    </row>
-    <row r="45" spans="1:28" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="38"/>
-      <c r="B45" s="39"/>
-      <c r="C45" s="39"/>
-      <c r="D45" s="40"/>
-      <c r="E45" s="40"/>
-      <c r="F45" s="40"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="40"/>
-      <c r="K45" s="60"/>
-      <c r="L45" s="60"/>
-      <c r="M45" s="60"/>
-      <c r="N45" s="41"/>
-      <c r="Q45" s="7"/>
-      <c r="AB45" s="19"/>
-    </row>
-    <row r="46" spans="1:28" s="10" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="42" t="s">
+      <c r="J48" s="84"/>
+      <c r="K48" s="85"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="120" t="s">
+        <v>18</v>
+      </c>
+      <c r="N48" s="86"/>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="18"/>
+      <c r="R48" s="9"/>
+      <c r="S48" s="18"/>
+    </row>
+    <row r="49" spans="1:19" s="10" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="79"/>
+      <c r="B49" s="82"/>
+      <c r="C49" s="82"/>
+      <c r="D49" s="82"/>
+      <c r="E49" s="82"/>
+      <c r="F49" s="82"/>
+      <c r="G49" s="82"/>
+      <c r="H49" s="82"/>
+      <c r="I49" s="82"/>
+      <c r="J49" s="82"/>
+      <c r="K49" s="83"/>
+      <c r="L49" s="81"/>
+      <c r="M49" s="81"/>
+      <c r="N49" s="80"/>
+      <c r="P49" s="9"/>
+      <c r="Q49" s="18"/>
+      <c r="R49" s="9"/>
+      <c r="S49" s="18"/>
+    </row>
+    <row r="50" spans="1:19" s="10" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="B46" s="43"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="44"/>
-      <c r="K46" s="141"/>
-      <c r="L46" s="141"/>
-      <c r="M46" s="141"/>
-      <c r="N46" s="45"/>
-      <c r="P46" s="9"/>
-      <c r="Q46" s="23"/>
-      <c r="R46" s="9"/>
-      <c r="S46" s="23"/>
-    </row>
-    <row r="47" spans="1:28" s="10" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="42"/>
-      <c r="B47" s="44"/>
-      <c r="C47" s="44"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="44"/>
-      <c r="I47" s="44"/>
-      <c r="J47" s="46"/>
-      <c r="K47" s="62"/>
-      <c r="L47" s="61"/>
-      <c r="M47" s="61"/>
-      <c r="N47" s="45"/>
-      <c r="P47" s="9"/>
-      <c r="Q47" s="23"/>
-      <c r="R47" s="9"/>
-      <c r="S47" s="23"/>
-    </row>
-    <row r="48" spans="1:28" s="10" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="42"/>
-      <c r="B48" s="44"/>
-      <c r="C48" s="44"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="44"/>
-      <c r="F48" s="44"/>
-      <c r="G48" s="44"/>
-      <c r="H48" s="44"/>
-      <c r="I48" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="J48" s="48"/>
-      <c r="K48" s="63"/>
-      <c r="L48" s="64"/>
-      <c r="M48" s="65" t="s">
-        <v>20</v>
-      </c>
-      <c r="N48" s="49"/>
-      <c r="P48" s="9"/>
-      <c r="Q48" s="23"/>
-      <c r="R48" s="9"/>
-      <c r="S48" s="23"/>
-    </row>
-    <row r="49" spans="1:19" s="10" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="50"/>
-      <c r="B49" s="51"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="51"/>
-      <c r="G49" s="51"/>
-      <c r="H49" s="51"/>
-      <c r="I49" s="51"/>
-      <c r="J49" s="52"/>
-      <c r="K49" s="66"/>
-      <c r="L49" s="67"/>
-      <c r="M49" s="67"/>
-      <c r="N49" s="53"/>
-      <c r="P49" s="9"/>
-      <c r="Q49" s="23"/>
-      <c r="R49" s="9"/>
-      <c r="S49" s="23"/>
-    </row>
-    <row r="50" spans="1:19" s="10" customFormat="1" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="B50" s="55"/>
-      <c r="C50" s="55"/>
-      <c r="D50" s="55"/>
-      <c r="E50" s="55"/>
-      <c r="F50" s="55"/>
-      <c r="G50" s="55"/>
-      <c r="H50" s="55"/>
-      <c r="I50" s="55"/>
-      <c r="J50" s="55"/>
-      <c r="K50" s="68"/>
-      <c r="L50" s="68"/>
-      <c r="M50" s="68"/>
-      <c r="N50" s="56"/>
+      <c r="B50" s="87"/>
+      <c r="C50" s="87"/>
+      <c r="D50" s="87"/>
+      <c r="E50" s="87"/>
+      <c r="F50" s="87"/>
+      <c r="G50" s="87"/>
+      <c r="H50" s="87"/>
+      <c r="I50" s="87"/>
+      <c r="J50" s="87"/>
+      <c r="K50" s="88"/>
+      <c r="L50" s="88"/>
+      <c r="M50" s="88"/>
+      <c r="N50" s="89"/>
       <c r="P50" s="9"/>
-      <c r="Q50" s="23"/>
+      <c r="Q50" s="18"/>
       <c r="R50" s="9"/>
-      <c r="S50" s="23"/>
+      <c r="S50" s="18"/>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A51" s="57"/>
-      <c r="B51" s="57"/>
-      <c r="C51" s="57"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="57"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="57"/>
-      <c r="K51" s="69"/>
-      <c r="L51" s="69"/>
-      <c r="M51" s="69"/>
-      <c r="N51" s="57"/>
+      <c r="A51" s="19"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+      <c r="M51" s="20"/>
+      <c r="N51" s="19"/>
     </row>
     <row r="52" spans="1:19" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="57"/>
-      <c r="B52" s="57"/>
-      <c r="C52" s="57"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="57"/>
-      <c r="F52" s="57"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="57"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="57"/>
-      <c r="K52" s="70"/>
-      <c r="L52" s="70"/>
-      <c r="M52" s="70"/>
-      <c r="N52" s="57"/>
+      <c r="A52" s="19"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="19"/>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A53" s="57"/>
-      <c r="B53" s="57"/>
-      <c r="C53" s="57"/>
-      <c r="D53" s="57"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="57"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="57"/>
-      <c r="K53" s="70"/>
-      <c r="L53" s="70"/>
-      <c r="M53" s="70"/>
-      <c r="N53" s="57"/>
+      <c r="A53" s="19"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="19"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="19"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="21"/>
+      <c r="M53" s="21"/>
+      <c r="N53" s="19"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="J54" s="19"/>
+      <c r="J54" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="65">
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:I2"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="K10:M11"/>
+    <mergeCell ref="N10:N11"/>
+    <mergeCell ref="K1:L2"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="A3:J4"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="K39:M39"/>
     <mergeCell ref="K41:M41"/>
     <mergeCell ref="K42:M42"/>
     <mergeCell ref="K46:M46"/>
@@ -4168,79 +3909,23 @@
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="K36:M36"/>
     <mergeCell ref="K33:M33"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="A3:J4"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:I2"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="K10:M11"/>
-    <mergeCell ref="N10:N11"/>
-    <mergeCell ref="K1:L2"/>
   </mergeCells>
-  <phoneticPr fontId="35" type="noConversion"/>
+  <phoneticPr fontId="32" type="noConversion"/>
   <conditionalFormatting sqref="A12:N12">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>'TRUE'</formula>
+      <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A7:I7" xr:uid="{AC32E5F5-8381-497F-BC25-1F820D6DA12A}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="0.39370078740157483" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="40" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="39" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AC32E5F5-8381-497F-BC25-1F820D6DA12A}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>A7:I7</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
